--- a/data/模板_咖啡题库导入.xlsx
+++ b/data/模板_咖啡题库导入.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -1639,9 +1639,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1684,9 +1682,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -1876,138 +1872,164 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>3. 上传方式</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   打开 https://coffee-quiz-djc.pages.dev</t>
+          <t>1.5 编码格式（重要）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">   首页找到"📥 批量加题"区</t>
+          <t xml:space="preserve">   - CSV 文件支持 UTF-8、UTF-8 BOM、GBK、GB18030</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">   选择 Excel 文件 → 预览 → 输密码 → 确认上传</t>
+          <t xml:space="preserve">   - 中文 Excel 默认保存为 GBK，直接上传也能正常解析</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">   30 秒后云端自动部署，所有人都能看到新题</t>
+          <t xml:space="preserve">   - 不需要手动转码，浏览器自动探测</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 推荐：保存时选 "CSV UTF-8（逗号分隔）" 兼容性最好</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4. 注意事项</t>
+          <t>3. 上传方式</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 上传后立即覆盖线上的题库</t>
+          <t xml:space="preserve">   打开 https://coffee-quiz-djc.pages.dev</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 错误填的题目会被跳过并在结果里说明</t>
+          <t xml:space="preserve">   首页找到"📥 批量加题"区</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 一次最多 500 道（多了请分批）</t>
+          <t xml:space="preserve">   选择 Excel 文件 → 预览 → 输密码 → 确认上传</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 旧题不会被删除（如果想替换题库用 git 直接改）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
+          <t xml:space="preserve">   30 秒后云端自动部署，所有人都能看到新题</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5. 字段长度建议</t>
+          <t>4. 注意事项</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 章节：≤ 20 字</t>
+          <t xml:space="preserve">   - 上传后立即覆盖线上的题库</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 题目：≤ 200 字</t>
+          <t xml:space="preserve">   - 错误填的题目会被跳过并在结果里说明</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 选项：≤ 100 字</t>
+          <t xml:space="preserve">   - 一次最多 500 道（多了请分批）</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>6. 模板示例：本表共 30 行示例（点击"题库导入模板" sheet 查看）</t>
-        </is>
-      </c>
-    </row>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 旧题不会被删除（如果想替换题库用 git 直接改）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5. 字段长度建议</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7. 不要在本表里加合计/说明行，导入器只读取从第 2 行开始的数据</t>
+          <t xml:space="preserve">   - 章节：≤ 20 字</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 题目：≤ 200 字</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 选项：≤ 100 字</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6. 模板示例：本表共 30 行示例（点击"题库导入模板" sheet 查看）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7. 不要在本表里加合计/说明行，导入器只读取从第 2 行开始的数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>最后更新：2026-10-08</t>
         </is>
